--- a/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
+++ b/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/ccs/BCS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\ccs\BCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F268FE25-6FA1-4964-97BE-7705BD55074C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE6FF5AB-5B37-43D8-9A34-98ECC3416F7E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1813C12-AB56-46B8-BBF3-88B137DBC055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8520" yWindow="2835" windowWidth="19200" windowHeight="11205" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -171,7 +171,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -182,7 +182,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -516,7 +515,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -612,120 +611,122 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" customWidth="1"/>
     <col min="2" max="2" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="2">
         <v>2021</v>
       </c>
-      <c r="C1" s="2">
+      <c r="D1" s="2">
         <v>2022</v>
       </c>
-      <c r="D1" s="2">
+      <c r="E1" s="2">
         <v>2023</v>
       </c>
-      <c r="E1" s="2">
+      <c r="F1" s="2">
         <v>2024</v>
       </c>
-      <c r="F1" s="2">
+      <c r="G1" s="2">
         <v>2025</v>
       </c>
-      <c r="G1" s="2">
+      <c r="H1" s="2">
         <v>2026</v>
       </c>
-      <c r="H1" s="2">
+      <c r="I1" s="2">
         <v>2027</v>
       </c>
-      <c r="I1" s="2">
+      <c r="J1" s="2">
         <v>2028</v>
       </c>
-      <c r="J1" s="2">
+      <c r="K1" s="2">
         <v>2029</v>
       </c>
-      <c r="K1" s="2">
+      <c r="L1" s="2">
         <v>2030</v>
       </c>
-      <c r="L1" s="2">
+      <c r="M1" s="2">
         <v>2031</v>
       </c>
-      <c r="M1" s="2">
+      <c r="N1" s="2">
         <v>2032</v>
       </c>
-      <c r="N1" s="2">
+      <c r="O1" s="2">
         <v>2033</v>
       </c>
-      <c r="O1" s="2">
+      <c r="P1" s="2">
         <v>2034</v>
       </c>
-      <c r="P1" s="2">
+      <c r="Q1" s="2">
         <v>2035</v>
       </c>
-      <c r="Q1" s="2">
+      <c r="R1" s="2">
         <v>2036</v>
       </c>
-      <c r="R1" s="2">
+      <c r="S1" s="2">
         <v>2037</v>
       </c>
-      <c r="S1" s="2">
+      <c r="T1" s="2">
         <v>2038</v>
       </c>
-      <c r="T1" s="2">
+      <c r="U1" s="2">
         <v>2039</v>
       </c>
-      <c r="U1" s="2">
+      <c r="V1" s="2">
         <v>2040</v>
       </c>
-      <c r="V1" s="2">
+      <c r="W1" s="2">
         <v>2041</v>
       </c>
-      <c r="W1" s="2">
+      <c r="X1" s="2">
         <v>2042</v>
       </c>
-      <c r="X1" s="2">
+      <c r="Y1" s="2">
         <v>2043</v>
       </c>
-      <c r="Y1" s="2">
+      <c r="Z1" s="2">
         <v>2044</v>
       </c>
-      <c r="Z1" s="2">
+      <c r="AA1" s="2">
         <v>2045</v>
       </c>
-      <c r="AA1" s="2">
+      <c r="AB1" s="2">
         <v>2046</v>
       </c>
-      <c r="AB1" s="2">
+      <c r="AC1" s="2">
         <v>2047</v>
       </c>
-      <c r="AC1" s="2">
+      <c r="AD1" s="2">
         <v>2048</v>
       </c>
-      <c r="AD1" s="2">
+      <c r="AE1" s="2">
         <v>2049</v>
       </c>
-      <c r="AE1" s="2">
+      <c r="AF1" s="2">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" s="4">
         <v>0</v>
       </c>
-      <c r="D2">
-        <f>About!$B$12*About!$A$10</f>
+      <c r="D2" s="4">
         <v>0</v>
       </c>
       <c r="E2">
@@ -765,6 +766,7 @@
         <v>0</v>
       </c>
       <c r="N2">
+        <f>About!$B$12*About!$A$10</f>
         <v>0</v>
       </c>
       <c r="O2">
@@ -818,19 +820,21 @@
       <c r="AE2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
       </c>
-      <c r="D3">
-        <f>About!$B$12*About!$A$10</f>
+      <c r="D3" s="4">
         <v>0</v>
       </c>
       <c r="E3">
@@ -870,6 +874,7 @@
         <v>0</v>
       </c>
       <c r="N3">
+        <f>About!$B$12*About!$A$10</f>
         <v>0</v>
       </c>
       <c r="O3">
@@ -921,6 +926,9 @@
         <v>0</v>
       </c>
       <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
         <v>0</v>
       </c>
     </row>
@@ -934,105 +942,108 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>14</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1040,19 +1051,18 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <f>$B$2</f>
         <v>0</v>
       </c>
       <c r="D2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:AE2" si="0">$B$2</f>
+        <f>$C$2</f>
         <v>0</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F2:AF2" si="0">$C$2</f>
         <v>0</v>
       </c>
       <c r="G2">
@@ -1152,6 +1162,10 @@
         <v>0</v>
       </c>
       <c r="AE2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1162,6 +1176,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -1305,29 +1334,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B93425-FCD2-45AD-8275-B76D4316592B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0612B897-9E6B-415C-B5ED-1A5707D32A0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CAB1C50-F8BD-4623-AF82-BA0216F7F2B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CAB1C50-F8BD-4623-AF82-BA0216F7F2B2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0612B897-9E6B-415C-B5ED-1A5707D32A0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B93425-FCD2-45AD-8275-B76D4316592B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>